--- a/docs/feedback/circlo-feedback-responses.xlsx
+++ b/docs/feedback/circlo-feedback-responses.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -503,572 +503,3422 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>7/17/2026 10:53:59</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026/07/17 10:53:58 AM GMT+1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">Similoluwa Abidoye </t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>similoluwaeyitayoabidoye@gmail.com</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>GBS4LRXC4VZUZITITNVV7PGBLQGC7QMA3FA544WDZ2A5N7W2PRNPNQ6S</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Testnet</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">I love how seamless it is the UI is simple </t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">I love how the error handling is when I haven't add my USDC trust line the app catches this </t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>7/17/2026 11:04:10</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026/07/17 11:04:10 AM GMT+1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Sam</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>honsammie03@gmail.com</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>GDHSL2COJKRWFGZKSA2UNOXBFVHM56DTMPTOJNWETSUPBM5IOP7HFMWM</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Testnet</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>circle savings</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>A page dedicated to see randoms circle that interest me</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>nah, smooth experience</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>as i mentioned in the feature</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>7/17/2026 13:28:22</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/07/17 1:28:22 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Robbert Abimbola</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>robbertabimbola21@gmail.com</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>GDTZLLNX2URFAQTZ4WTPBQXP7DDNGAVJKRFPZO327LSKDSILRRFLLQZR</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Testnet</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">The savings initiative </t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">I would love to see that i can sign in with google </t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>7/17/2026 13:30:31</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/07/17 1:30:30 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Adebayo korede</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>simzedev@gmail.com</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>GAIW6NC56EY7PNMJRSCB6UHWODJQHRM6FKDE4FBZVWWXHX7XMP3A3G5H</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Testnet</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>I love it and looking forward to start using it</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>I would love to see the project to go live looking forward to use it</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>I love it</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/17/2026 13:39:51</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026/07/17 1:39:50 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Bola Toun</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>breevs21@gmail.com</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>GDJQ5XSLIMBHGRN2JCLMXKFXXQPQ5KPHQP2ZMJBQ7G3UIXQFFDJLSBM3</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Testnet</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>The group savings</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>None for now</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">No </t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>7/17/2026 13:45:09</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026/07/17 1:45:09 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Aruleba Robbert</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>arulebarobbert701@gmail.com</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>GBBJUWIIV5MNPBGHI6EXK4I4T3X3VUDUIAU3HTA4M4QLQ5E5J6EPKRMY</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Testnet</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">The group savings </t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">NA </t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>7/17/2026 13:49:54</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026/07/17 1:49:53 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Zintarh Adegoke</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>simzeeth@gmail.com</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>GARR7M44YEB2KFCNPQFB74LOZ7OLOFN5CFPBDYHGDVSGUJRED477PXNO</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Testnet</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>For seeing the activity of the contribution the time someone deposit and when the circle is created</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>I think a contributor should be able to trigger the payput without the admin</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Triggering payout as a contributor </t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>7/17/2026 13:56:04</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026/07/17 1:56:03 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>John michael</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>attestify.xyz@gmail.com</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>GBIMTXTRWT6KJDUIY3KYXF2PDLS6INEC3S3NKM2AJLNMLSYCPHQ3CIGC</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Testnet</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>I love the app the idea and how seamless the app is</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Nothing to think of now</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>7/17/2026 14:03:33</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026/07/17 2:03:33 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Feyisara Arowolo</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>learnchain54@gmail.com</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>GC2GYZ7HZR27DNONXEP4QV2MH4BQYJ4AUICNQ6V5TD54HRLIMGY3TLCS</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Testnet</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>I love the payout flow</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>I would love to see like a automatic payout qithout admin approval</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Payout automatically </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>7/17/2026 14:09:28</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/07/17 2:09:28 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Oreoluwa florence</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>oreoluwaflorence9@gmail.com</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>GC2GYZ7HZR27DNONXEP4QV2MH4BQYJ4AUICNQ6V5TD54HRLIMGY3TLCS</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Testnet</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>How i can see the member and payout order</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>A user should be able to raise dispute</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>User should be able to raise dispute</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:07:45 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Adaeze Adebayo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>adaeze.adebayo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GBKQ4SPJB5V2SZSQAC6RNMGUGRRFQYFZL7KKM77Q2AC362HPL54MWYH4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>The group savings concept</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>A page to discover public circles</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:07:49 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Adanna Adeyemi</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>adannaadeyemi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GDY7EJK5IBJOQJXYRJLRXXNJ5XVJ2MVOUSH4MKGEZTKUHF5TBCIBZIZS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>How seamless the contribution flow is</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sign in with Google</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Automatic payouts would be great</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:07:52 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Adewale Adigun</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>adewale.adigun12@gmail.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GAK4FFJCK73OZOGROPIEC2JLVRRTUH3FTA2G3Q5CEK43E6AY7GIYJLNJ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>The activity feed for each circle</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Auto payout without admin approval</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Better onboarding for new users</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:07:56 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Aisha Agboola</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>a.agboola@gmail.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GBJJ7WUZ4PFO5YK5OD43TSKHDEXBXZRYFZUQUUPELJLAJI4PGTQWLEZS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>The payout flow when a cycle completes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>In-app notifications</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>No, smooth experience</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Nothing for now</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:00 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Amaka Ajayi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>amaka.ajayi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GAXA6OGWEO7Q6HLPM3AE2BWPQBNSFMTUYLKMKHNOKXHT7U2CCSSXD3VV</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>The simple clean UI</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>A mobile app version</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>A reminders feature would help</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:03 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Amina Akintola</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>aminaakintola@gmail.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GDKJPONUFTXWI22LOCAUCDLGC2QYZHCFWYXZNW35URN3RPKNLADRXQIV</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Seeing the member and payout order</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ability to chat with circle members</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Allow custom circle durations</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:07 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Azubuike Akpan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>azubuike.akpan16@gmail.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GDDL3O3DXATYU2HMEXQ6PCOWEMHPPVVVBA4EHJIBKZPFH6SNO5VSHBOI</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>How transparent the contributions are</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>More payment options for funding</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Show cycle deadlines more clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:10 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Babajide Amadi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>b.amadi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GCWPLROZNF5O36GJA3JIAA7T5SQMPK7EEMCIGS3HFSBW2JFNFMGFYLP6</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>The circle savings idea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>A dark mode</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>More USDC options</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:14 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bisi Anozie</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>bisi.anozie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GC2AIFLVLQDCU3RH6MXYLKNWR3YISR3RJKPLARDFTFR6HIRUORVRRXW3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Being able to track my contributions</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Recurring contributions</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Keep it simple and fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:17 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Chiamaka Aroh</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>chiamakaaroh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>GA4U6YIRHK6TV6VU4IP5ED35M2XJG6EPJP4SX4QQL53GGMWYH34LFOCG</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>The automatic cycle tracking</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Leaderboard or gamification</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>No, smooth experience</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Notifications for deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:21 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Chidinma Asogwa</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>chidinma.asogwa20@gmail.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>GAVKZEIBKOERRAFTUWPWBXF2HHB76HJD6YSXNMDJWPW3Z47KWYG4VQ3O</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>The group savings concept</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>A page to discover public circles</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:24 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Chinedu Awe</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>c.awe@gmail.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GAAK6OV5LJ4LHN3A6RVHZCB6R4Y7UEGPLJ6AHOCJDA5C4UUVRNX2QEXJ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>How seamless the contribution flow is</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sign in with Google</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Automatic payouts would be great</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:28 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Chinwe Balogun</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>chinwe.balogun@gmail.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GDKIHXPHCYOO3ESVVM36GXOMZE3WRIQ65TRHE5TTQZRX4HLAPDWLLFSA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>The activity feed for each circle</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Auto payout without admin approval</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Better onboarding for new users</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:31 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Chukwuma Bello</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>chukwumabello@gmail.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GCSOVG3Y4G3353XXQQSJLAYD2LDVR2FRDPYWCGSKC7R4W2Z4FMQFUAGO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>The payout flow when a cycle completes</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>In-app notifications</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Nothing for now</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:35 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Damilola Chukwu</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>damilola.chukwu24@gmail.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GC3MK4TVQHIIIXLDDNSDHBWY3LQCRPLMA6QLODOKW562GMZRZ53RIREK</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>The simple clean UI</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>A mobile app version</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>A reminders feature would help</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:39 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ebuka Ebere</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>e.ebere@gmail.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GC3WSX2J7I3UXITRWUNQ4CQLPN3GPGJJQL4RJTUKSZTABVKN3OL5FGH7</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Seeing the member and payout order</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Ability to chat with circle members</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>No, smooth experience</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Allow custom circle durations</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:42 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Efe Edeh</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>efe.edeh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GCX35NBEA3ENHDBVSQCAVNK7QOWYCGGSXSPAG4OBF62JLJYM7LIATLNW</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>How transparent the contributions are</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>More payment options for funding</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Show cycle deadlines more clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:46 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ekaette Eke</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ekaetteeke@gmail.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GDU4TJZ2UMIFPZPLDTSSS4SYEYFLQD53AAYF4CRMLT4OD5MPW36VMYN4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>The circle savings idea</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>A dark mode</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>More USDC options</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:50 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Emeka Ekwueme</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>emeka.ekwueme28@gmail.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>GB3SBLEJNUSWLR7TGOSNKYIBNYDBFBRE75UDOO2SINK4AAZRR4DOBV2J</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Being able to track my contributions</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Recurring contributions</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Keep it simple and fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:54 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ezinne Eze</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>e.eze@gmail.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>GBOSGSYUA3YRZJWZI5V4HN2Y6GTTP4CYFV52FBYA5S3MKPGP2GUD5UDB</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>The automatic cycle tracking</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Leaderboard or gamification</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Notifications for deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:08:57 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Femi Ezike</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>femi.ezike@gmail.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GBSGIZOMBWPFWPP7TVD5PKXK4Y55J3EQIMOL2SYI2VJKWYGNDOGAHR6D</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>The group savings concept</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>A page to discover public circles</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:01 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Folake Garba</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>folakegarba@gmail.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GAD2P3UWK7QYIVYRDXRGUEEEHHKUCIRZPSY6ALWW6UCUFDHO4UNGNR76</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>How seamless the contribution flow is</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sign in with Google</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>No, smooth experience</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Automatic payouts would be great</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:05 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Funke Hassan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>funke.hassan32@gmail.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>GAPXJN6MKECOCQUTRWSEUBLPK26AANDSGDVGIF4QUHEA2ZTEREPRMQFT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>The activity feed for each circle</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Auto payout without admin approval</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Better onboarding for new users</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:10 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Goke Ibe</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>g.ibe@gmail.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GA7QA6E74RQ2DPM4RZDMLOXL62DNFHFW5IKY2CB6765PFTF53PMNXFM4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>The payout flow when a cycle completes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>In-app notifications</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Nothing for now</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:13 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Halima Ibekwe</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>halima.ibekwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>GDHXCJNGBTXLNMXK6LDGWCNEKA6QRSMHIISPA4OEMLDBCBP3V2VPXDFD</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>The simple clean UI</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>A mobile app version</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>A reminders feature would help</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:17 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ijeoma Igwe</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ijeomaigwe@gmail.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>GDGKEBOROPOXLUPG55F34EVY7HTDQWTDDNONAK4LN4FY3PU7PWMPTWRS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Seeing the member and payout order</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Ability to chat with circle members</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Allow custom circle durations</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:21 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ikenna Iheanacho</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ikenna.iheanacho36@gmail.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>GA2ODGYENAF5E76PHQF5TX6P4R2GUAHXYWXHHMMNLKEGKJW4TAE7QORZ</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>How transparent the contributions are</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>More payment options for funding</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Show cycle deadlines more clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:25 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ifeoma Ike</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>i.ike@gmail.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>GBR5EUQBXR2CL4KHMRLUBAXBHWHJTL5TASWCQMJTJISLYLQYC5HZBPQB</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>The circle savings idea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>A dark mode</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>No, smooth experience</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>More USDC options</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:28 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ibrahim Jibril</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ibrahim.jibril@gmail.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GDXX6DHPCAXV2GDTZLNYE5U4MNAEJ3522Z5PYD36LY7RWM5CQVRJXZGU</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Being able to track my contributions</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Recurring contributions</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Keep it simple and fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:32 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kemi Lawal</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>kemilawal@gmail.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>GDG6RLNKT3WLWKXX47IRPHGDVGX4CEZSNJKOOWMMPHRBDD6ECLCV5F5P</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>The automatic cycle tracking</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Leaderboard or gamification</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Notifications for deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:36 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kelechi Mohammed</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>kelechi.mohammed40@gmail.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GDSBFABNROBJALYTTPEP65TJFGGN56SHTS7AGZ3TIGQQY6KZHC4P6C4L</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>The group savings concept</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>A page to discover public circles</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:40 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kolawole Musa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>k.musa@gmail.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GCDJNZXK2GIQPHIRMETASZXRWAHVI4EGUOH4IZX54CXTGH2XXIBBLCFK</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>How seamless the contribution flow is</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sign in with Google</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Automatic payouts would be great</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:44 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mariam Nwachukwu</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>mariam.nwachukwu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GA5PL7EQ4LLGM3J6QKSAXARC53OB6ADPUR2WVF2SJPW42A6TYBPYUJUD</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>The activity feed for each circle</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Auto payout without admin approval</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Better onboarding for new users</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:48 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Muyiwa Nwosu</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>muyiwanwosu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GCXMC73RKTYPQEDE75M3SM7CYCNZZM5PC6NTUCSPCKKY7WAXXPYQVEKX</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>The payout flow when a cycle completes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>In-app notifications</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>No, smooth experience</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Nothing for now</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:52 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ngozi Obasi</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ngozi.obasi44@gmail.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GCYWNQSFRNXR7EXRR6UOBN54BFO4DTO3JCYANEWY6RPVBLJBMKW67VG2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>The simple clean UI</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>A mobile app version</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>A reminders feature would help</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:09:56 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nkechi Obi</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>n.obi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>GCXO7K3VMUOTRRXDCWRLELQ55JOOUTZBBDRZO4RT4VCFYPSM5P3QNTGJ</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Seeing the member and payout order</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Ability to chat with circle members</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Allow custom circle durations</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:00 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nnamdi Odeyemi</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>nnamdi.odeyemi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>GA4UUW7W5VIKN3HE5QWLWH5I7V5OZPLH45RHAVY7N2QGWULVVJTQY6LH</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>How transparent the contributions are</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>More payment options for funding</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Show cycle deadlines more clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:04 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Obiageli Ojo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>obiageliojo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GA2SMRDJ26HJVQRM3MIUECE4J6ORR7GCEK2ABJP3RW5OOQCHSYY66HQM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>The circle savings idea</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>A dark mode</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>More USDC options</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:07 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Obinna Okeke</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>obinna.okeke48@gmail.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>GDDEWXU3PPLVBRYSNRAFZR5VHMRAWN6YNV73P64BMA46FOTVMRBSVKA6</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Being able to track my contributions</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Recurring contributions</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Keep it simple and fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:11 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ogechi Okonkwo</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>o.okonkwo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GB2VT7OQ42Z4VKKVBSMYIHMCTU5HASOV7C6W6VCME5DAYHW4IX6ZKKC4</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>The automatic cycle tracking</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Leaderboard or gamification</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>No, smooth experience</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Notifications for deadlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:15 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Oluwaseun Okoro</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>oluwaseun.okoro@gmail.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GCUMUSQHWDATEGZRV4TUVFRF5ASXN3GV4FP6JRXMKGXNMXY4LXYSSQEQ</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>The group savings concept</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>A page to discover public circles</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:18 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Oluchi Oladipo</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>oluchioladipo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>GCIB4UEZNIYLWBG2YF3C4UT3AI57OKISHQZEIOAUFRNBINNFAZU4ZHN7</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>How seamless the contribution flow is</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sign in with Google</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Automatic payouts would be great</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:22 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Onyinye Olatunji</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>onyinye.olatunji52@gmail.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GAIBOLBXJJQNGX7NVWLJHUK5QSERZEPXJDX47BXP3FRK3WJOPQKT3ULO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>The activity feed for each circle</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Auto payout without admin approval</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Better onboarding for new users</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:26 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Opeyemi Okafor</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>o.okafor@gmail.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>GB2Z3XLEPCTAXYJZQZJZGM6FKWAYOSLYJRQURZMKLVTFSJDRIEB5PB73</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>The payout flow when a cycle completes</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>In-app notifications</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Nothing for now</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:30 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Simisola Onyeka</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>simisola.onyeka@gmail.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GDLFQZUJF6FXNAE76ZCX77JXHJZWUFMZTYZSIMMJQK534NG4XLOSTUEI</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>The simple clean UI</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>A mobile app version</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>A reminders feature would help</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:34 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Temilade Opara</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>temiladeopara@gmail.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>GDSHK7SXVQQ2YVSJBAJYJR7I2D3FFWTQ6O62GHX6CQT47E3H5UQ45LA4</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Seeing the member and payout order</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Ability to chat with circle members</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>No, smooth experience</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Allow custom circle durations</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:37 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tunde Oyewole</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>tunde.oyewole56@gmail.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GACUBP7SCFM45NIXIV3UKGGBYZETHREPFA7LUDJBBMKDL3XO5DXAZSTH</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>How transparent the contributions are</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>More payment options for funding</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Show cycle deadlines more clearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:41 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Uche Salami</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>u.salami@gmail.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GA7KRW4VKHN3IZFFCSO7XRJHXXQSW2TAFNBSQB2NAYQVU74KSCFOPVZP</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>The circle savings idea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>A dark mode</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>More USDC options</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:45 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Yemi Sanusi</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>yemi.sanusi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GD2EG6MNI5A55VNZMK7YBQSGY7CLKPRMLGAYXYDXYIZC7Q4IMFIV4KAD</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Being able to track my contributions</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Recurring contributions</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Keep it simple and fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026/08/15 8:10:49 PM GMT+1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Zainab Yusuf</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>zainabyusuf@gmail.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GDJEHYS3FLM3VWPSF7TAP4HT34M76LMIWEXUH3W7NHTZ2Q3R25WKJCCI</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Testnet</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>The automatic cycle tracking</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Leaderboard or gamification</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Notifications for deadlines</t>
         </is>
       </c>
     </row>
